--- a/output/xlsform_hab1-4.xlsx
+++ b/output/xlsform_hab1-4.xlsx
@@ -35311,7 +35311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35883,12 +35883,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>afw</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>afw.</t>
         </is>
       </c>
     </row>
@@ -35900,12 +35900,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>zs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>zs (&lt;3 ex.)</t>
         </is>
       </c>
     </row>
@@ -35917,12 +35917,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>s</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>s (4-10 ex.)</t>
         </is>
       </c>
     </row>
@@ -35934,12 +35934,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>wt</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>wt (10-50 ex.)</t>
         </is>
       </c>
     </row>
@@ -35951,12 +35951,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5_10perc</t>
+          <t>t</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5-10%</t>
+          <t>t (&gt;50 ex.)</t>
         </is>
       </c>
     </row>
@@ -35968,12 +35968,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10_20perc</t>
+          <t>5_10perc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10-20%</t>
+          <t>5-10</t>
         </is>
       </c>
     </row>
@@ -35985,12 +35985,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20_30perc</t>
+          <t>10_20perc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>20-30%</t>
+          <t>10-20</t>
         </is>
       </c>
     </row>
@@ -36002,12 +36002,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_40perc</t>
+          <t>20_30perc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>30-40%</t>
+          <t>20-30</t>
         </is>
       </c>
     </row>
@@ -36019,12 +36019,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>40_50perc</t>
+          <t>30_40perc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>40-50%</t>
+          <t>30-40</t>
         </is>
       </c>
     </row>
@@ -36036,12 +36036,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>50_60perc</t>
+          <t>40_50perc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>50-60%</t>
+          <t>40-50</t>
         </is>
       </c>
     </row>
@@ -36053,12 +36053,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>60_70perc</t>
+          <t>50_60perc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>60-70%</t>
+          <t>50-60</t>
         </is>
       </c>
     </row>
@@ -36070,12 +36070,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>70_80perc</t>
+          <t>60_70perc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>70-80%</t>
+          <t>60-70</t>
         </is>
       </c>
     </row>
@@ -36087,12 +36087,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>80_90perc</t>
+          <t>70_80perc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>80-90%</t>
+          <t>70-80</t>
         </is>
       </c>
     </row>
@@ -36104,12 +36104,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>90_95perc</t>
+          <t>80_90perc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-90</t>
         </is>
       </c>
     </row>
@@ -36121,29 +36121,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>95_100perc</t>
+          <t>90_95perc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>lijst_subhabitats</t>
+          <t>LSVI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>95_100perc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>95-100</t>
         </is>
       </c>
     </row>
@@ -36155,12 +36155,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2130_had</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2130_HAD</t>
+          <t>2110</t>
         </is>
       </c>
     </row>
@@ -36172,12 +36172,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2130_had</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2130_HAD</t>
         </is>
       </c>
     </row>
@@ -36189,12 +36189,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>2310</t>
         </is>
       </c>
     </row>
@@ -36206,12 +36206,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4010</t>
         </is>
       </c>
     </row>
@@ -36223,12 +36223,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2330_bu</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2330_BU</t>
+          <t>4030</t>
         </is>
       </c>
     </row>
@@ -36240,12 +36240,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2330_dw</t>
+          <t>2330_bu</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2330_DW</t>
+          <t>2330_BU</t>
         </is>
       </c>
     </row>
@@ -36257,12 +36257,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2130_hd</t>
+          <t>2330_dw</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2130_HD</t>
+          <t>2330_DW</t>
         </is>
       </c>
     </row>
@@ -36274,12 +36274,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2130_hd</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2130_HD</t>
         </is>
       </c>
     </row>
@@ -36291,12 +36291,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2150</t>
         </is>
       </c>
     </row>
@@ -36308,12 +36308,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2160</t>
         </is>
       </c>
     </row>
@@ -36325,12 +36325,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2170</t>
         </is>
       </c>
     </row>
@@ -36342,12 +36342,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2190_mp</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2190_MP</t>
+          <t>2180</t>
         </is>
       </c>
     </row>
@@ -36359,12 +36359,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2190_mp</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2190_MP</t>
         </is>
       </c>
     </row>
@@ -36376,12 +36376,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3130_aom</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3130_AOM</t>
+          <t>3110</t>
         </is>
       </c>
     </row>
@@ -36393,12 +36393,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3130_na</t>
+          <t>3130_aom</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3130_NA</t>
+          <t>3130_AOM</t>
         </is>
       </c>
     </row>
@@ -36410,12 +36410,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3130_na</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3130_NA</t>
         </is>
       </c>
     </row>
@@ -36427,12 +36427,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3140</t>
         </is>
       </c>
     </row>
@@ -36444,12 +36444,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3150</t>
         </is>
       </c>
     </row>
@@ -36461,12 +36461,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3160</t>
         </is>
       </c>
     </row>
@@ -36478,12 +36478,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3260</t>
         </is>
       </c>
     </row>
@@ -36495,12 +36495,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1310_zv</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1310_ZV</t>
+          <t>3270</t>
         </is>
       </c>
     </row>
@@ -36512,12 +36512,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1310_zk</t>
+          <t>1310_zv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1310_ZK</t>
+          <t>1310_ZV</t>
         </is>
       </c>
     </row>
@@ -36529,12 +36529,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1310_zk</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1310_ZK</t>
         </is>
       </c>
     </row>
@@ -36546,12 +36546,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1330_da</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1330_DA</t>
+          <t>1320</t>
         </is>
       </c>
     </row>
@@ -36563,12 +36563,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1330_hpr</t>
+          <t>1330_da</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1330_HPR</t>
+          <t>1330_DA</t>
         </is>
       </c>
     </row>
@@ -36580,12 +36580,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1330_hpr</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1330_HPR</t>
         </is>
       </c>
     </row>
@@ -36597,12 +36597,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2190_a</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2190_A</t>
+          <t>2120</t>
         </is>
       </c>
     </row>
@@ -36614,10 +36614,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>2190_a</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2190_A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>lijst_subhabitats</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>1310_pol</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>1310_POL</t>
         </is>
